--- a/reports/集团总公司_资产负债表_2025-05.xlsx
+++ b/reports/集团总公司_资产负债表_2025-05.xlsx
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0</v>
+        <v>6526000</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0</v>
+        <v>6630416</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0</v>
+        <v>6968000</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0</v>
+        <v>7079488</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0</v>
+        <v>7852000</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0</v>
+        <v>7977632</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0</v>
+        <v>10504000</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0</v>
+        <v>10672064</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0</v>
+        <v>10946000</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0</v>
+        <v>11121136</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0</v>
+        <v>11388000</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0</v>
+        <v>11570208</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0</v>
+        <v>13598000</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0</v>
+        <v>13815568</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>499500000</v>
+        <v>567282000</v>
       </c>
       <c r="G29" s="19" t="n"/>
     </row>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0</v>
+        <v>18018000</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0</v>
+        <v>18306288</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="F55" s="19" t="n">
-        <v>2159000000</v>
+        <v>2177018000</v>
       </c>
       <c r="G55" s="19" t="n"/>
     </row>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="F56" s="19" t="n">
-        <v>2658500000</v>
+        <v>2744300000</v>
       </c>
       <c r="G56" s="19" t="n"/>
     </row>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="F60" s="16" t="n">
-        <v>0</v>
+        <v>30836000</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>0</v>
+        <v>31329376</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1">
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="F62" s="16" t="n">
-        <v>0</v>
+        <v>31720000</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>0</v>
+        <v>32227520</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0</v>
+        <v>34372000</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0</v>
+        <v>34921952</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1">
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0</v>
+        <v>34814000</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0</v>
+        <v>35371024</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="F70" s="16" t="n">
-        <v>0</v>
+        <v>35256000</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0</v>
+        <v>35820096</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="F78" s="16" t="n">
-        <v>0</v>
+        <v>38792000</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>0</v>
+        <v>39412672</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1">
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0</v>
+        <v>39234000</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0</v>
+        <v>39861744</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="F84" s="19" t="n">
-        <v>338000000</v>
+        <v>583024000</v>
       </c>
       <c r="G84" s="19" t="n"/>
     </row>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="F86" s="16" t="n">
-        <v>0</v>
+        <v>42328000</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>0</v>
+        <v>43005248</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1">
@@ -5238,7 +5238,7 @@
         </is>
       </c>
       <c r="F98" s="19" t="n">
-        <v>529000000</v>
+        <v>571328000</v>
       </c>
       <c r="G98" s="19" t="n"/>
     </row>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="F99" s="19" t="n">
-        <v>867000000</v>
+        <v>1154352000</v>
       </c>
       <c r="G99" s="19" t="n"/>
     </row>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="F121" s="16" t="n">
-        <v>316500000</v>
+        <v>114948000</v>
       </c>
       <c r="G121" s="16" t="n">
         <v>560768952</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="F122" s="19" t="n">
-        <v>1791500000</v>
+        <v>1589948000</v>
       </c>
       <c r="G122" s="19" t="n"/>
     </row>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="F124" s="19" t="n">
-        <v>1791500000</v>
+        <v>1589948000</v>
       </c>
       <c r="G124" s="19" t="n"/>
     </row>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="F125" s="25" t="n">
-        <v>2658500000</v>
+        <v>2744300000</v>
       </c>
       <c r="G125" s="25" t="n"/>
     </row>
